--- a/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
+++ b/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.4781643011829615</v>
+        <v>0.45630816353267</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.04258639396614965</v>
+        <v>0.04437004750051631</v>
       </c>
     </row>
     <row r="12">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.1808024634415262</v>
+        <v>0.1883750452665103</v>
       </c>
     </row>
     <row r="13">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.2139060571318126</v>
+        <v>0.2228651226758185</v>
       </c>
     </row>
     <row r="14">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.08454078427755009</v>
+        <v>0.08808162102448482</v>
       </c>
     </row>
     <row r="15">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.4781643011829615</v>
+        <v>0.45630816353267</v>
       </c>
     </row>
     <row r="27">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.04258639396614965</v>
+        <v>0.04437004750051631</v>
       </c>
     </row>
     <row r="28">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.1808024634415262</v>
+        <v>0.1883750452665103</v>
       </c>
     </row>
     <row r="29">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.2139060571318126</v>
+        <v>0.2228651226758185</v>
       </c>
     </row>
     <row r="30">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.08454078427755009</v>
+        <v>0.08808162102448482</v>
       </c>
     </row>
     <row r="31">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.4781643011829615</v>
+        <v>0.45630816353267</v>
       </c>
     </row>
     <row r="43">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.04258639396614965</v>
+        <v>0.04437004750051631</v>
       </c>
     </row>
     <row r="44">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.1808024634415262</v>
+        <v>0.1883750452665103</v>
       </c>
     </row>
     <row r="45">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.2139060571318126</v>
+        <v>0.2228651226758185</v>
       </c>
     </row>
     <row r="46">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.08454078427755009</v>
+        <v>0.08808162102448482</v>
       </c>
     </row>
     <row r="47">
